--- a/product_selector_out/STM32F2x5.xlsx
+++ b/product_selector_out/STM32F2x5.xlsx
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -16189,7 +16189,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions (continued): V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F2x5.xlsx
+++ b/product_selector_out/STM32F2x5.xlsx
@@ -8434,14 +8434,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -8449,9 +8449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
@@ -8771,14 +8771,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -8786,9 +8786,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q13" s="10" t="inlineStr">
@@ -9108,14 +9108,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -9123,9 +9123,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">
@@ -9445,14 +9445,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -9460,9 +9460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
@@ -9782,14 +9782,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -9797,9 +9797,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
@@ -10119,14 +10119,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -10134,9 +10134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
@@ -10456,14 +10456,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -10471,9 +10471,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
@@ -10793,14 +10793,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -10808,9 +10808,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -11130,14 +11130,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -11145,9 +11145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
@@ -11467,14 +11467,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -11482,9 +11482,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
@@ -11804,14 +11804,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -11819,9 +11819,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q22" s="10" t="inlineStr">
@@ -12141,14 +12141,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
@@ -12156,9 +12156,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q23" s="10" t="inlineStr">
@@ -12478,14 +12478,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
@@ -12493,9 +12493,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q24" s="10" t="inlineStr">
@@ -12815,14 +12815,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -12830,9 +12830,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
@@ -13152,14 +13152,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -13167,9 +13167,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q26" s="10" t="inlineStr">
@@ -13489,14 +13489,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
@@ -13504,9 +13504,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q27" s="10" t="inlineStr">
@@ -13826,14 +13826,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -13841,9 +13841,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q28" s="10" t="inlineStr">
@@ -14163,14 +14163,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
@@ -14178,9 +14178,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
@@ -14500,14 +14500,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
@@ -14515,9 +14515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q30" s="10" t="inlineStr">
@@ -14837,14 +14837,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -14852,9 +14852,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr">

--- a/product_selector_out/STM32F2x5.xlsx
+++ b/product_selector_out/STM32F2x5.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO31"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.52734375" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="18" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -917,6 +918,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1014,6 +1020,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1348,6 +1355,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -1685,6 +1697,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2022,6 +2039,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2359,6 +2381,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -2696,6 +2723,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3033,6 +3065,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3370,6 +3407,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -3707,6 +3749,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4044,6 +4091,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4381,6 +4433,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -4718,6 +4775,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5055,6 +5117,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5392,6 +5459,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -5729,6 +5801,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f205rb.pdf</t>
         </is>
       </c>
@@ -6066,6 +6143,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -6403,6 +6485,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -6740,6 +6827,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -7077,6 +7169,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -7414,6 +7511,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
@@ -7751,12 +7853,17 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f215re.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AD10:AD11"/>
     <mergeCell ref="AU10:AU11"/>
@@ -7777,13 +7884,15 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="M10:N10"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="O10"/>
     <mergeCell ref="AC10:AC11"/>
@@ -7800,9 +7909,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AQ10:AR10"/>
     <mergeCell ref="I10:I11"/>
@@ -7858,7 +7966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO31"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7928,6 +8036,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8275,6 +8384,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8372,6 +8486,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8704,7 +8819,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9041,7 +9161,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9378,7 +9503,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9715,7 +9845,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10052,7 +10187,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10389,7 +10529,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10726,7 +10871,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11063,7 +11213,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11400,7 +11555,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11737,7 +11897,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12074,7 +12239,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12411,7 +12581,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12748,7 +12923,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13085,7 +13265,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13422,7 +13607,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13759,7 +13949,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14096,7 +14291,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14433,7 +14633,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14770,7 +14975,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15107,7 +15317,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15115,8 +15330,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
